--- a/data/argentina/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/argentina/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z17"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,1241 +558,1183 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>noM4eJv9</t>
+          <t>fotMKZ7K</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
-        <v>27.16296296296296</v>
-      </c>
-      <c r="D2" t="n">
-        <v>178.0666666666667</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1.107407407407407</v>
-      </c>
-      <c r="F2" t="n">
-        <v>70.9074074074074</v>
-      </c>
-      <c r="G2" t="n">
-        <v>2480740.740740741</v>
-      </c>
-      <c r="H2" t="n">
-        <v>73.7037037037037</v>
-      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>27.85185185185185</v>
+        <v>26.9790404040404</v>
       </c>
       <c r="J2" t="n">
-        <v>175.7037037037037</v>
+        <v>177.5767676767677</v>
       </c>
       <c r="K2" t="n">
-        <v>1.148148148148148</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>71.55555555555556</v>
+        <v>70.4128787878788</v>
       </c>
       <c r="M2" t="n">
-        <v>2891666.666666667</v>
+        <v>3041502.525252525</v>
       </c>
       <c r="N2" t="n">
-        <v>73.8888888888889</v>
+        <v>73.53232323232324</v>
       </c>
       <c r="O2" t="n">
-        <v>24.41805555555555</v>
+        <v>29.97333333333334</v>
       </c>
       <c r="P2" t="n">
-        <v>174.113425925926</v>
+        <v>177.88</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.072685185185185</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>65.91157407407407</v>
+        <v>66.52000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>1480254.62962963</v>
+        <v>695000</v>
       </c>
       <c r="T2" t="n">
-        <v>71.95601851851852</v>
+        <v>67.25333333333333</v>
       </c>
       <c r="U2" t="n">
-        <v>28.24166666666667</v>
+        <v>26.95279520020568</v>
       </c>
       <c r="V2" t="n">
-        <v>177.9375</v>
+        <v>178.4702570400141</v>
       </c>
       <c r="W2" t="n">
-        <v>1.225</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>68.98333333333333</v>
+        <v>70.04219407569791</v>
       </c>
       <c r="Y2" t="n">
-        <v>1364895.833333333</v>
+        <v>2381886.146970866</v>
       </c>
       <c r="Z2" t="n">
-        <v>72.675</v>
+        <v>73.46317034060002</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>nkx6zI2q</t>
+          <t>YHCv8dOE</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>24.80793650793651</v>
+      </c>
+      <c r="D3" t="n">
+        <v>179.1198412698413</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>66.73730158730159</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1425158.73015873</v>
+      </c>
+      <c r="H3" t="n">
+        <v>71.39126984126985</v>
+      </c>
       <c r="I3" t="n">
-        <v>24</v>
+        <v>25.9966588966589</v>
       </c>
       <c r="J3" t="n">
-        <v>178.925925925926</v>
+        <v>180.4968919968919</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>69.1111111111111</v>
+        <v>70.41616161616162</v>
       </c>
       <c r="M3" t="n">
-        <v>2338888.888888889</v>
+        <v>2743960.761460762</v>
       </c>
       <c r="N3" t="n">
-        <v>74.81481481481482</v>
+        <v>74.18523698523698</v>
       </c>
       <c r="O3" t="n">
-        <v>22.60622710622711</v>
+        <v>24.11363423761593</v>
       </c>
       <c r="P3" t="n">
-        <v>181.565934065934</v>
+        <v>176.8796477892817</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>68.45604395604396</v>
+        <v>65.95640679686447</v>
       </c>
       <c r="S3" t="n">
-        <v>2499557.387057387</v>
+        <v>1390023.886868281</v>
       </c>
       <c r="T3" t="n">
-        <v>74.92704517704517</v>
+        <v>71.42961139546952</v>
       </c>
       <c r="U3" t="n">
-        <v>23.83518518518519</v>
+        <v>24.01830421040948</v>
       </c>
       <c r="V3" t="n">
-        <v>178.3777777777778</v>
+        <v>179.6750866092971</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>67.86481481481482</v>
+        <v>69.37028410186305</v>
       </c>
       <c r="Y3" t="n">
-        <v>1868796.296296296</v>
+        <v>2680220.780681307</v>
       </c>
       <c r="Z3" t="n">
-        <v>73.24629629629629</v>
+        <v>75.16107547423336</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>pdWqnF1e</t>
+          <t>llkWcC07</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>26.4</v>
+        <v>26.58226495726496</v>
       </c>
       <c r="D4" t="n">
-        <v>177.8296296296296</v>
+        <v>180.3185897435897</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>1.026709401709402</v>
       </c>
       <c r="F4" t="n">
-        <v>69.41481481481482</v>
+        <v>68.01388888888889</v>
       </c>
       <c r="G4" t="n">
-        <v>1970370.37037037</v>
+        <v>1546223.290598291</v>
       </c>
       <c r="H4" t="n">
-        <v>72.84444444444443</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+        <v>71.55299145299145</v>
+      </c>
+      <c r="I4" t="n">
+        <v>27.41717171717171</v>
+      </c>
+      <c r="J4" t="n">
+        <v>180.2272727272727</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>69.56969696969696</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1606717.171717172</v>
+      </c>
+      <c r="N4" t="n">
+        <v>72.14646464646465</v>
+      </c>
       <c r="O4" t="n">
-        <v>24.55614035087719</v>
+        <v>27.68888938737337</v>
       </c>
       <c r="P4" t="n">
-        <v>176.368671679198</v>
+        <v>179.0966841733146</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>1.103605004834982</v>
       </c>
       <c r="R4" t="n">
-        <v>68.85664160401002</v>
+        <v>67.94754086493218</v>
       </c>
       <c r="S4" t="n">
-        <v>2859711.779448621</v>
+        <v>1461101.554814369</v>
       </c>
       <c r="T4" t="n">
-        <v>74.94135338345865</v>
+        <v>71.53641692975216</v>
       </c>
       <c r="U4" t="n">
-        <v>23.81328320802005</v>
+        <v>24.21385281385281</v>
       </c>
       <c r="V4" t="n">
-        <v>180.8934837092732</v>
+        <v>177.5220238095238</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>66.80075187969925</v>
+        <v>67.47012987012988</v>
       </c>
       <c r="Y4" t="n">
-        <v>1657644.110275689</v>
+        <v>1615647.772366523</v>
       </c>
       <c r="Z4" t="n">
-        <v>72.95112781954887</v>
+        <v>73.86016414141413</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>vq1qlyXr</t>
+          <t>hMeNaYVf</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>25.94006734006734</v>
+        <v>27.4375</v>
       </c>
       <c r="D5" t="n">
-        <v>180.7986531986532</v>
+        <v>178.21875</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>1.09375</v>
       </c>
       <c r="F5" t="n">
-        <v>70.18484848484849</v>
+        <v>72.625</v>
       </c>
       <c r="G5" t="n">
-        <v>2561978.114478115</v>
+        <v>3141406.25</v>
       </c>
       <c r="H5" t="n">
-        <v>74.03602693602693</v>
+        <v>74.5</v>
       </c>
       <c r="I5" t="n">
-        <v>23.71296296296296</v>
+        <v>26.072668997669</v>
       </c>
       <c r="J5" t="n">
-        <v>177.6851851851852</v>
+        <v>177.0419774669775</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>67.23148148148148</v>
+        <v>67.99459984459985</v>
       </c>
       <c r="M5" t="n">
-        <v>1948495.37037037</v>
+        <v>1522596.639471639</v>
       </c>
       <c r="N5" t="n">
-        <v>72.01388888888889</v>
+        <v>72.23741258741258</v>
       </c>
       <c r="O5" t="n">
-        <v>24.01957671957672</v>
+        <v>25.34139584484853</v>
       </c>
       <c r="P5" t="n">
-        <v>180.2746031746032</v>
+        <v>177.1860367112285</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>1.036987046769656</v>
       </c>
       <c r="R5" t="n">
-        <v>69.06243386243386</v>
+        <v>71.34996705482639</v>
       </c>
       <c r="S5" t="n">
-        <v>2377447.08994709</v>
+        <v>2872882.68707706</v>
       </c>
       <c r="T5" t="n">
-        <v>74.57671957671958</v>
+        <v>74.95387152631397</v>
       </c>
       <c r="U5" t="n">
-        <v>24.55894638557177</v>
+        <v>25.04127277404869</v>
       </c>
       <c r="V5" t="n">
-        <v>175.4282274313234</v>
+        <v>177.3488600437095</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>66.36448965551132</v>
+        <v>66.69506456382712</v>
       </c>
       <c r="Y5" t="n">
-        <v>1352453.437515357</v>
+        <v>1325981.717093757</v>
       </c>
       <c r="Z5" t="n">
-        <v>70.7749766573296</v>
+        <v>70.85964003295108</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>U9B9fwfF</t>
+          <t>trGn6zgR</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>26.96666666666667</v>
+        <v>25.022113997114</v>
       </c>
       <c r="D6" t="n">
-        <v>181.1333333333333</v>
+        <v>178.3125721500722</v>
       </c>
       <c r="E6" t="n">
-        <v>1.033333333333333</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>70.06666666666666</v>
+        <v>69.96075036075037</v>
       </c>
       <c r="G6" t="n">
-        <v>2049166.666666667</v>
+        <v>2934225.108225108</v>
       </c>
       <c r="H6" t="n">
-        <v>74</v>
+        <v>74.82380952380952</v>
       </c>
       <c r="I6" t="n">
-        <v>25.77777777777778</v>
+        <v>23.82927350427351</v>
       </c>
       <c r="J6" t="n">
-        <v>176.8888888888889</v>
+        <v>178.959188034188</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>70</v>
+        <v>67.41944444444445</v>
       </c>
       <c r="M6" t="n">
-        <v>2877777.777777778</v>
+        <v>1955170.94017094</v>
       </c>
       <c r="N6" t="n">
-        <v>74.33333333333333</v>
+        <v>72.7034188034188</v>
       </c>
       <c r="O6" t="n">
-        <v>24.78042328042328</v>
+        <v>26.70331117374024</v>
       </c>
       <c r="P6" t="n">
-        <v>177.6772486772487</v>
+        <v>175.2266725669026</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.063492063492063</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>68.93650793650794</v>
+        <v>69.29622131800737</v>
       </c>
       <c r="S6" t="n">
-        <v>2144907.407407408</v>
+        <v>2053284.891461196</v>
       </c>
       <c r="T6" t="n">
-        <v>75.06349206349206</v>
+        <v>73.44939503788017</v>
       </c>
       <c r="U6" t="n">
-        <v>26.62996031746032</v>
+        <v>23.92897992100779</v>
       </c>
       <c r="V6" t="n">
-        <v>175.7073412698413</v>
+        <v>178.4318978579041</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>69.14781746031746</v>
+        <v>66.11688120531001</v>
       </c>
       <c r="Y6" t="n">
-        <v>1755009.920634921</v>
+        <v>1544781.615121205</v>
       </c>
       <c r="Z6" t="n">
-        <v>73.01587301587301</v>
+        <v>70.84458676858058</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>KvUIXFn2</t>
+          <t>badJ0EGl</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>27.55925925925926</v>
+        <v>26.14398148148148</v>
       </c>
       <c r="D7" t="n">
-        <v>180.3407407407408</v>
+        <v>178.0199074074074</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>1.016666666666667</v>
       </c>
       <c r="F7" t="n">
-        <v>68.67777777777779</v>
+        <v>70.11412037037037</v>
       </c>
       <c r="G7" t="n">
-        <v>1606111.111111111</v>
+        <v>2591701.388888889</v>
       </c>
       <c r="H7" t="n">
-        <v>71.47037037037036</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+        <v>74.26620370370371</v>
+      </c>
+      <c r="I7" t="n">
+        <v>26.28484848484848</v>
+      </c>
+      <c r="J7" t="n">
+        <v>177.3920875420876</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.073063973063973</v>
+      </c>
+      <c r="L7" t="n">
+        <v>69.03998316498316</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2031929.713804714</v>
+      </c>
+      <c r="N7" t="n">
+        <v>72.79688552188551</v>
+      </c>
       <c r="O7" t="n">
-        <v>25.53899240855762</v>
+        <v>24.27081663275995</v>
       </c>
       <c r="P7" t="n">
-        <v>177.7159247757074</v>
+        <v>176.9505113472963</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>68.08928571428571</v>
+        <v>68.84510216966754</v>
       </c>
       <c r="S7" t="n">
-        <v>1889212.387853692</v>
+        <v>2491642.101091732</v>
       </c>
       <c r="T7" t="n">
-        <v>72.59411663216009</v>
+        <v>74.52806381229578</v>
       </c>
       <c r="U7" t="n">
-        <v>25.05550887021475</v>
+        <v>23.55459343288291</v>
       </c>
       <c r="V7" t="n">
-        <v>176.7782913165266</v>
+        <v>175.503223311776</v>
       </c>
       <c r="W7" t="n">
-        <v>1.015873015873016</v>
+        <v>1.036753524253524</v>
       </c>
       <c r="X7" t="n">
-        <v>70.93398692810457</v>
+        <v>65.96570030846345</v>
       </c>
       <c r="Y7" t="n">
-        <v>2554570.494864612</v>
+        <v>1588151.329664488</v>
       </c>
       <c r="Z7" t="n">
-        <v>75.0688608776844</v>
+        <v>72.81919666590719</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bPuAZyIk</t>
+          <t>2iHr7GwL</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="n">
-        <v>24.875</v>
-      </c>
-      <c r="D8" t="n">
-        <v>176.625</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" t="n">
-        <v>66</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1281250</v>
-      </c>
-      <c r="H8" t="n">
-        <v>71.625</v>
-      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>26.46759259259259</v>
+        <v>28.49722222222222</v>
       </c>
       <c r="J8" t="n">
-        <v>180.1296296296296</v>
+        <v>181.4180555555556</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>1.576157407407408</v>
       </c>
       <c r="L8" t="n">
-        <v>67.56018518518518</v>
+        <v>74.17986111111112</v>
       </c>
       <c r="M8" t="n">
-        <v>1410069.444444445</v>
+        <v>4472569.444444445</v>
       </c>
       <c r="N8" t="n">
-        <v>71</v>
+        <v>77.18055555555556</v>
       </c>
       <c r="O8" t="n">
-        <v>25.51520467836258</v>
+        <v>25.85294705294705</v>
       </c>
       <c r="P8" t="n">
-        <v>180.9754385964912</v>
+        <v>176.6448717948718</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.137816764132554</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>65.74307992202728</v>
+        <v>66.65149017649017</v>
       </c>
       <c r="S8" t="n">
-        <v>1005908.382066277</v>
+        <v>1182765.151515151</v>
       </c>
       <c r="T8" t="n">
-        <v>70.43976608187134</v>
+        <v>71.13910256410257</v>
       </c>
       <c r="U8" t="n">
-        <v>27.82373737373737</v>
+        <v>25.63644281048616</v>
       </c>
       <c r="V8" t="n">
-        <v>180.0025252525253</v>
+        <v>177.8747491961083</v>
       </c>
       <c r="W8" t="n">
-        <v>1.174242424242424</v>
+        <v>1.144027330083058</v>
       </c>
       <c r="X8" t="n">
-        <v>67.6969696969697</v>
+        <v>71.0524563522706</v>
       </c>
       <c r="Y8" t="n">
-        <v>1352121.212121212</v>
+        <v>3507808.36353762</v>
       </c>
       <c r="Z8" t="n">
-        <v>71.37373737373737</v>
+        <v>76.71730043148</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>tlVEYeXe</t>
+          <t>WCfRbho1</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>27.29629629629629</v>
+        <v>27.47850168350168</v>
       </c>
       <c r="D9" t="n">
-        <v>180.5185185185185</v>
+        <v>178.9690067340067</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>1.05526936026936</v>
       </c>
       <c r="F9" t="n">
-        <v>69.07407407407406</v>
+        <v>73.5627946127946</v>
       </c>
       <c r="G9" t="n">
-        <v>1477777.777777778</v>
+        <v>5348928.451178451</v>
       </c>
       <c r="H9" t="n">
-        <v>71.85185185185185</v>
+        <v>76.66621212121213</v>
       </c>
       <c r="I9" t="n">
-        <v>27.58240740740741</v>
+        <v>27.17008547008547</v>
       </c>
       <c r="J9" t="n">
-        <v>178.7416666666667</v>
+        <v>180.6324786324786</v>
       </c>
       <c r="K9" t="n">
-        <v>1.075</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>72.77592592592593</v>
+        <v>68.75299145299147</v>
       </c>
       <c r="M9" t="n">
-        <v>5138157.407407408</v>
+        <v>1670277.777777778</v>
       </c>
       <c r="N9" t="n">
-        <v>75.55833333333334</v>
+        <v>71.57948717948717</v>
       </c>
       <c r="O9" t="n">
-        <v>24.26136363636364</v>
+        <v>25.49397097266662</v>
       </c>
       <c r="P9" t="n">
-        <v>176.4305555555556</v>
+        <v>177.9886148440931</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>1.15591756070017</v>
       </c>
       <c r="R9" t="n">
-        <v>67.75631313131315</v>
+        <v>72.22264004433571</v>
       </c>
       <c r="S9" t="n">
-        <v>1705239.898989899</v>
+        <v>5116384.142041534</v>
       </c>
       <c r="T9" t="n">
-        <v>73.99621212121212</v>
+        <v>76.59392925110318</v>
       </c>
       <c r="U9" t="n">
-        <v>27.28787878787879</v>
+        <v>25.8302269989796</v>
       </c>
       <c r="V9" t="n">
-        <v>179.665404040404</v>
+        <v>177.5869840461681</v>
       </c>
       <c r="W9" t="n">
-        <v>1.21969696969697</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>73.5239898989899</v>
+        <v>67.7595618849916</v>
       </c>
       <c r="Y9" t="n">
-        <v>4913914.141414142</v>
+        <v>1703670.600901803</v>
       </c>
       <c r="Z9" t="n">
-        <v>76.62626262626263</v>
+        <v>72.23819577871831</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>xzFHhHOR</t>
+          <t>vJVmoZG1</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>30.375</v>
+        <v>24.91576879910214</v>
       </c>
       <c r="D10" t="n">
-        <v>181.875</v>
+        <v>178.957379349046</v>
       </c>
       <c r="E10" t="n">
-        <v>1.875</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>74.875</v>
+        <v>66.09988776655445</v>
       </c>
       <c r="G10" t="n">
-        <v>3962500</v>
+        <v>1335912.317620651</v>
       </c>
       <c r="H10" t="n">
-        <v>76.625</v>
+        <v>71.41837822671157</v>
       </c>
       <c r="I10" t="n">
-        <v>24.61111111111111</v>
+        <v>25.79691358024691</v>
       </c>
       <c r="J10" t="n">
-        <v>178</v>
+        <v>181.2388888888889</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>66.97222222222223</v>
+        <v>68.22376543209877</v>
       </c>
       <c r="M10" t="n">
-        <v>1496527.777777778</v>
+        <v>1640401.234567901</v>
       </c>
       <c r="N10" t="n">
-        <v>71.94444444444444</v>
+        <v>71.94876543209877</v>
       </c>
       <c r="O10" t="n">
-        <v>26.55436720142602</v>
+        <v>23.71442388021335</v>
       </c>
       <c r="P10" t="n">
-        <v>178.6257957728546</v>
+        <v>177.7444653299917</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.169467787114846</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>70.53323147440796</v>
+        <v>65.81477732793522</v>
       </c>
       <c r="S10" t="n">
-        <v>2745409.982174688</v>
+        <v>1438686.013912988</v>
       </c>
       <c r="T10" t="n">
-        <v>75.64514896867838</v>
+        <v>72.42485862091125</v>
       </c>
       <c r="U10" t="n">
-        <v>24.15711462450593</v>
+        <v>24.27035023456076</v>
       </c>
       <c r="V10" t="n">
-        <v>177.3883399209486</v>
+        <v>180.7452921548563</v>
       </c>
       <c r="W10" t="n">
         <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>65.83300395256917</v>
+        <v>66.15962467079638</v>
       </c>
       <c r="Y10" t="n">
-        <v>1382633.399209486</v>
+        <v>1573933.848762177</v>
       </c>
       <c r="Z10" t="n">
-        <v>71.33300395256917</v>
+        <v>72.63152549258051</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>rDFDgc9L</t>
+          <t>fRDz9x98</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>23.95833333333333</v>
+        <v>25.02083333333333</v>
       </c>
       <c r="D11" t="n">
-        <v>179.2083333333333</v>
+        <v>177.1037037037037</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>67.08333333333333</v>
+        <v>67.95694444444445</v>
       </c>
       <c r="G11" t="n">
-        <v>1952083.333333333</v>
+        <v>1971313.657407407</v>
       </c>
       <c r="H11" t="n">
-        <v>71.91666666666667</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+        <v>71.63958333333333</v>
+      </c>
+      <c r="I11" t="n">
+        <v>25.39720279720279</v>
+      </c>
+      <c r="J11" t="n">
+        <v>180.813986013986</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>66.95034965034966</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1291153.846153846</v>
+      </c>
+      <c r="N11" t="n">
+        <v>70.41398601398602</v>
+      </c>
       <c r="O11" t="n">
-        <v>24.31851851851852</v>
+        <v>25.54111094730289</v>
       </c>
       <c r="P11" t="n">
-        <v>179.6888888888889</v>
+        <v>176.1719176506328</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>66.34444444444445</v>
+        <v>66.29832930514044</v>
       </c>
       <c r="S11" t="n">
-        <v>1496296.296296296</v>
+        <v>1201854.588193598</v>
       </c>
       <c r="T11" t="n">
-        <v>70.60000000000001</v>
+        <v>69.72888350183241</v>
       </c>
       <c r="U11" t="n">
-        <v>23.14848484848484</v>
+        <v>23.99581735621782</v>
       </c>
       <c r="V11" t="n">
-        <v>176.4333333333333</v>
+        <v>178.0567105189073</v>
       </c>
       <c r="W11" t="n">
         <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>65.87272727272726</v>
+        <v>66.04041325654597</v>
       </c>
       <c r="Y11" t="n">
-        <v>1303787.878787879</v>
+        <v>1415256.102434306</v>
       </c>
       <c r="Z11" t="n">
-        <v>73.2</v>
+        <v>71.63031830065012</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>U9kvubfS</t>
+          <t>hMZipgW7</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>27.25462962962963</v>
+        <v>26.46666666666667</v>
       </c>
       <c r="D12" t="n">
-        <v>178.6157407407407</v>
+        <v>179.1032828282828</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>70.3425925925926</v>
+        <v>67.24520202020202</v>
       </c>
       <c r="G12" t="n">
-        <v>2891898.148148148</v>
+        <v>1300042.929292929</v>
       </c>
       <c r="H12" t="n">
-        <v>73.07407407407408</v>
+        <v>72.00580808080808</v>
       </c>
       <c r="I12" t="n">
-        <v>23.125</v>
+        <v>25.6937908496732</v>
       </c>
       <c r="J12" t="n">
-        <v>178.75</v>
+        <v>178.0771241830065</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>65.5625</v>
+        <v>69.87924836601306</v>
       </c>
       <c r="M12" t="n">
-        <v>1443750</v>
+        <v>2244297.385620915</v>
       </c>
       <c r="N12" t="n">
-        <v>71.9375</v>
+        <v>74.05114379084968</v>
       </c>
       <c r="O12" t="n">
-        <v>26.62222222222222</v>
+        <v>24.137723314697</v>
       </c>
       <c r="P12" t="n">
-        <v>178.3813725490196</v>
+        <v>178.9596965169333</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>69.34542483660131</v>
+        <v>65.71495324850588</v>
       </c>
       <c r="S12" t="n">
-        <v>2276813.725490196</v>
+        <v>1199703.766628109</v>
       </c>
       <c r="T12" t="n">
-        <v>73.63496732026144</v>
+        <v>71.45817588843904</v>
       </c>
       <c r="U12" t="n">
-        <v>23.63876319758673</v>
+        <v>24.61187512102418</v>
       </c>
       <c r="V12" t="n">
-        <v>177.7096530920061</v>
+        <v>177.6340412359853</v>
       </c>
       <c r="W12" t="n">
         <v>1</v>
       </c>
       <c r="X12" t="n">
-        <v>65.7733785822021</v>
+        <v>68.68102257017756</v>
       </c>
       <c r="Y12" t="n">
-        <v>1296910.350678733</v>
+        <v>2250701.210952133</v>
       </c>
       <c r="Z12" t="n">
-        <v>70.90422322775264</v>
+        <v>74.12414361751686</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>jJjztvuM</t>
+          <t>nPhF1f1r</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="C13" t="n">
+        <v>28.47037037037037</v>
+      </c>
+      <c r="D13" t="n">
+        <v>177.2348148148148</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.124444444444445</v>
+      </c>
+      <c r="F13" t="n">
+        <v>71.82222222222222</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3015981.481481482</v>
+      </c>
+      <c r="H13" t="n">
+        <v>74.20148148148148</v>
+      </c>
+      <c r="I13" t="n">
+        <v>28.03057498057499</v>
+      </c>
+      <c r="J13" t="n">
+        <v>180.7992618492619</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.111519036519037</v>
+      </c>
+      <c r="L13" t="n">
+        <v>71.05260295260295</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2216594.794094794</v>
+      </c>
+      <c r="N13" t="n">
+        <v>73.97228049728049</v>
+      </c>
       <c r="O13" t="n">
-        <v>29.88888888888889</v>
+        <v>27.08992079957553</v>
       </c>
       <c r="P13" t="n">
-        <v>178.7555555555556</v>
+        <v>178.3813470204135</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>1.172303378633302</v>
       </c>
       <c r="R13" t="n">
-        <v>66.67777777777778</v>
+        <v>68.89509703851138</v>
       </c>
       <c r="S13" t="n">
-        <v>715000</v>
+        <v>1722495.507476326</v>
       </c>
       <c r="T13" t="n">
-        <v>67.05555555555556</v>
+        <v>72.77920857914465</v>
       </c>
       <c r="U13" t="n">
-        <v>23.02380952380952</v>
+        <v>24.96782717031586</v>
       </c>
       <c r="V13" t="n">
-        <v>177.6765873015873</v>
+        <v>177.3944159912486</v>
       </c>
       <c r="W13" t="n">
-        <v>1</v>
+        <v>1.055736495781745</v>
       </c>
       <c r="X13" t="n">
-        <v>65.56150793650794</v>
+        <v>69.30535693567369</v>
       </c>
       <c r="Y13" t="n">
-        <v>1474255.952380952</v>
+        <v>2336616.569704805</v>
       </c>
       <c r="Z13" t="n">
-        <v>73.2063492063492</v>
+        <v>75.0125376383295</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>8fN0daP2</t>
+          <t>trxILFhE</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>26.65656565656566</v>
+        <v>23.46111111111111</v>
       </c>
       <c r="D14" t="n">
-        <v>177.1346801346801</v>
+        <v>179.1708333333333</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>67.54882154882155</v>
+        <v>65.76944444444445</v>
       </c>
       <c r="G14" t="n">
-        <v>1335858.585858586</v>
+        <v>1444236.111111111</v>
       </c>
       <c r="H14" t="n">
-        <v>71.28619528619528</v>
+        <v>71.8875</v>
       </c>
       <c r="I14" t="n">
-        <v>26.26851851851852</v>
+        <v>25.72777777777778</v>
       </c>
       <c r="J14" t="n">
-        <v>177.5462962962963</v>
+        <v>179.5166666666667</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>69.98611111111113</v>
+        <v>71.37222222222222</v>
       </c>
       <c r="M14" t="n">
-        <v>2326620.37037037</v>
+        <v>3096388.888888889</v>
       </c>
       <c r="N14" t="n">
-        <v>74.02777777777779</v>
+        <v>75.27777777777777</v>
       </c>
       <c r="O14" t="n">
-        <v>24.44814814814815</v>
+        <v>23.65501720417674</v>
       </c>
       <c r="P14" t="n">
-        <v>178.1777777777778</v>
+        <v>177.8936302193529</v>
       </c>
       <c r="Q14" t="n">
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>66.52222222222223</v>
+        <v>65.3872456117341</v>
       </c>
       <c r="S14" t="n">
-        <v>1339074.074074074</v>
+        <v>1253173.684796558</v>
       </c>
       <c r="T14" t="n">
-        <v>70.76666666666667</v>
+        <v>70.90064740368364</v>
       </c>
       <c r="U14" t="n">
-        <v>24.57502546473135</v>
+        <v>22.86609369388781</v>
       </c>
       <c r="V14" t="n">
-        <v>176.5509994907054</v>
+        <v>180.3475892408245</v>
       </c>
       <c r="W14" t="n">
         <v>1</v>
       </c>
       <c r="X14" t="n">
-        <v>69.31285332314744</v>
+        <v>68.23489693313222</v>
       </c>
       <c r="Y14" t="n">
-        <v>2911391.170104405</v>
+        <v>2323057.952668247</v>
       </c>
       <c r="Z14" t="n">
-        <v>74.52869238604532</v>
+        <v>74.2603086619263</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>65Xumenk</t>
+          <t>Y9EiyTMr</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>25.55151515151515</v>
+        <v>23.32569444444444</v>
       </c>
       <c r="D15" t="n">
-        <v>180.7909090909091</v>
+        <v>178.8041666666666</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>67.41818181818182</v>
+        <v>69.36250000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>1389621.212121212</v>
+        <v>2920937.5</v>
       </c>
       <c r="H15" t="n">
-        <v>70.7060606060606</v>
+        <v>75.48472222222222</v>
       </c>
       <c r="I15" t="n">
-        <v>25.03472222222222</v>
+        <v>27.17008547008547</v>
       </c>
       <c r="J15" t="n">
-        <v>178.9236111111111</v>
+        <v>180.6324786324786</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>66.40972222222223</v>
+        <v>68.75299145299147</v>
       </c>
       <c r="M15" t="n">
-        <v>1283506.944444444</v>
+        <v>1670277.777777778</v>
       </c>
       <c r="N15" t="n">
-        <v>72.34027777777777</v>
+        <v>71.57948717948717</v>
       </c>
       <c r="O15" t="n">
-        <v>24.08575757575757</v>
+        <v>23.67741934144073</v>
       </c>
       <c r="P15" t="n">
-        <v>179.0893939393939</v>
+        <v>177.2816028708134</v>
       </c>
       <c r="Q15" t="n">
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>67.35424242424243</v>
+        <v>68.12453141613503</v>
       </c>
       <c r="S15" t="n">
-        <v>1740053.03030303</v>
+        <v>1965815.149853801</v>
       </c>
       <c r="T15" t="n">
-        <v>72.19787878787879</v>
+        <v>73.59304259702286</v>
       </c>
       <c r="U15" t="n">
-        <v>24.24074074074074</v>
+        <v>25.8302269989796</v>
       </c>
       <c r="V15" t="n">
-        <v>176.8468915343915</v>
+        <v>177.5869840461681</v>
       </c>
       <c r="W15" t="n">
         <v>1</v>
       </c>
       <c r="X15" t="n">
-        <v>66.78505291005291</v>
+        <v>67.7595618849916</v>
       </c>
       <c r="Y15" t="n">
-        <v>1370634.920634921</v>
+        <v>1703670.600901803</v>
       </c>
       <c r="Z15" t="n">
-        <v>71.98511904761905</v>
+        <v>72.23819577871831</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>SvlzcWFD</t>
+          <t>fgvPVMI8</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
-      <c r="C16" t="n">
-        <v>24</v>
-      </c>
-      <c r="D16" t="n">
-        <v>178.925925925926</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="n">
-        <v>69.1111111111111</v>
-      </c>
-      <c r="G16" t="n">
-        <v>2338888.888888889</v>
-      </c>
-      <c r="H16" t="n">
-        <v>74.81481481481482</v>
-      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>24.875</v>
+        <v>26.46666666666667</v>
       </c>
       <c r="J16" t="n">
-        <v>176.625</v>
+        <v>179.1032828282828</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>66</v>
+        <v>67.24520202020202</v>
       </c>
       <c r="M16" t="n">
-        <v>1281250</v>
+        <v>1300042.929292929</v>
       </c>
       <c r="N16" t="n">
-        <v>71.625</v>
-      </c>
-      <c r="O16" t="n">
-        <v>23.83518518518519</v>
-      </c>
-      <c r="P16" t="n">
-        <v>178.3777777777778</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>67.86481481481482</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1868796.296296296</v>
-      </c>
-      <c r="T16" t="n">
-        <v>73.24629629629629</v>
-      </c>
+        <v>72.00580808080808</v>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
       <c r="U16" t="n">
-        <v>25.51520467836258</v>
+        <v>24.137723314697</v>
       </c>
       <c r="V16" t="n">
-        <v>180.9754385964912</v>
+        <v>178.9596965169333</v>
       </c>
       <c r="W16" t="n">
-        <v>1.137816764132554</v>
+        <v>1</v>
       </c>
       <c r="X16" t="n">
-        <v>65.74307992202728</v>
+        <v>65.71495324850588</v>
       </c>
       <c r="Y16" t="n">
-        <v>1005908.382066277</v>
+        <v>1199703.766628109</v>
       </c>
       <c r="Z16" t="n">
-        <v>70.43976608187134</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>ngdGLTFj</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="n">
-        <v>25.77777777777778</v>
-      </c>
-      <c r="D17" t="n">
-        <v>176.8888888888889</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" t="n">
-        <v>70</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2877777.777777778</v>
-      </c>
-      <c r="H17" t="n">
-        <v>74.33333333333333</v>
-      </c>
-      <c r="I17" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="J17" t="n">
-        <v>177.8296296296296</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>69.41481481481482</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1970370.37037037</v>
-      </c>
-      <c r="N17" t="n">
-        <v>72.84444444444443</v>
-      </c>
-      <c r="O17" t="n">
-        <v>26.62996031746032</v>
-      </c>
-      <c r="P17" t="n">
-        <v>175.7073412698413</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>69.14781746031746</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1755009.920634921</v>
-      </c>
-      <c r="T17" t="n">
-        <v>73.01587301587301</v>
-      </c>
-      <c r="U17" t="n">
-        <v>24.55614035087719</v>
-      </c>
-      <c r="V17" t="n">
-        <v>176.368671679198</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1</v>
-      </c>
-      <c r="X17" t="n">
-        <v>68.85664160401002</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2859711.779448621</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>74.94135338345865</v>
+        <v>71.45817588843904</v>
       </c>
     </row>
   </sheetData>
